--- a/intern_schedule_2026-2027/schedules/TYP_December_2026.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_December_2026.xlsx
@@ -517,17 +517,17 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>BRONSON, VIVEKANANDAN</t>
+          <t>BRONSON I, VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>SHETTY</t>
+          <t>SHETTY K</t>
         </is>
       </c>
     </row>
@@ -542,17 +542,17 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, VIVEKANANDAN</t>
+          <t>MACNEILLE S, VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>SHETTY</t>
+          <t>SHETTY K</t>
         </is>
       </c>
     </row>
@@ -567,17 +567,17 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN</t>
+          <t>VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>SHETTY</t>
+          <t>SHETTY K</t>
         </is>
       </c>
     </row>
@@ -592,17 +592,17 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>BRONSON, VIVEKANANDAN</t>
+          <t>BRONSON I, VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>SHETTY</t>
+          <t>SHETTY K</t>
         </is>
       </c>
     </row>
@@ -617,13 +617,13 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN</t>
+          <t>VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN  (24H)</t>
+          <t>VIVEKANANDAN S  (24H)</t>
         </is>
       </c>
     </row>
@@ -638,13 +638,13 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>SHETTY</t>
+          <t>SHETTY K</t>
         </is>
       </c>
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
     </row>
@@ -659,17 +659,17 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>VILLANUEVA, VIVEKANANDAN</t>
+          <t>VILLANUEVA R, VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
     </row>
@@ -684,17 +684,17 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>VILLANUEVA R</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>BRONSON, VIVEKANANDAN</t>
+          <t>BRONSON I, VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
     </row>
@@ -709,17 +709,17 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN</t>
+          <t>VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>BRONSON, VILLANUEVA</t>
+          <t>BRONSON I, VILLANUEVA R</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
     </row>
@@ -734,17 +734,17 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>VILLANUEVA R</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN</t>
+          <t>VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
     </row>
@@ -759,17 +759,17 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>VILLANUEVA, VIVEKANANDAN</t>
+          <t>VILLANUEVA R, VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
     </row>
@@ -784,13 +784,13 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>VILLANUEVA R</t>
         </is>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>VILLANUEVA  (24H)</t>
+          <t>VILLANUEVA R  (24H)</t>
         </is>
       </c>
     </row>
@@ -805,13 +805,13 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN</t>
+          <t>VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="D15" s="5" t="n"/>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -826,17 +826,17 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>VILLANUEVA, SALAM</t>
+          <t>VILLANUEVA R, SALAM M</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -851,17 +851,17 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>SALAM</t>
+          <t>SALAM M</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, VILLANUEVA</t>
+          <t>MACNEILLE S, VILLANUEVA R</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -876,17 +876,17 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>VILLANUEVA R</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, SALAM</t>
+          <t>MACNEILLE S, SALAM M</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -901,17 +901,17 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>SALAM</t>
+          <t>SALAM M</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>VILLANUEVA R</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -926,17 +926,17 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>VILLANUEVA R</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, SALAM</t>
+          <t>MACNEILLE S, SALAM M</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -951,13 +951,13 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
       <c r="D21" s="4" t="n"/>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE  (24H)</t>
+          <t>MACNEILLE S  (24H)</t>
         </is>
       </c>
     </row>
@@ -972,13 +972,13 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>VILLANUEVA R</t>
         </is>
       </c>
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>SALAM</t>
+          <t>SALAM M</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, FARZEELA</t>
+          <t>MACNEILLE S, FARZEELA F</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>SALAM</t>
+          <t>SALAM M</t>
         </is>
       </c>
     </row>
@@ -1018,17 +1018,17 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>FARZEELA</t>
+          <t>FARZEELA F</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, BRONSON</t>
+          <t>MACNEILLE S, BRONSON I</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>SALAM</t>
+          <t>SALAM M</t>
         </is>
       </c>
     </row>
@@ -1043,17 +1043,17 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>BRONSON, FARZEELA</t>
+          <t>BRONSON I, FARZEELA F</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>SALAM</t>
+          <t>SALAM M</t>
         </is>
       </c>
     </row>
@@ -1068,17 +1068,17 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>FARZEELA</t>
+          <t>FARZEELA F</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>SALAM</t>
+          <t>SALAM M</t>
         </is>
       </c>
     </row>
@@ -1093,17 +1093,17 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>BRONSON, FARZEELA</t>
+          <t>BRONSON I, FARZEELA F</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>SALAM</t>
+          <t>SALAM M</t>
         </is>
       </c>
     </row>
@@ -1118,13 +1118,13 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D28" s="4" t="n"/>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>BRONSON  (24H)</t>
+          <t>BRONSON I  (24H)</t>
         </is>
       </c>
     </row>
@@ -1139,13 +1139,13 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>SALAM</t>
+          <t>SALAM M</t>
         </is>
       </c>
       <c r="D29" s="5" t="n"/>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>FARZEELA</t>
+          <t>FARZEELA F</t>
         </is>
       </c>
     </row>
@@ -1160,17 +1160,17 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>BRONSON, SALAM</t>
+          <t>BRONSON I, SALAM M</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>FARZEELA</t>
+          <t>FARZEELA F</t>
         </is>
       </c>
     </row>
@@ -1185,17 +1185,17 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, SALAM</t>
+          <t>MACNEILLE S, SALAM M</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>FARZEELA</t>
+          <t>FARZEELA F</t>
         </is>
       </c>
     </row>
@@ -1210,17 +1210,17 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>SALAM</t>
+          <t>SALAM M</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, BRONSON</t>
+          <t>MACNEILLE S, BRONSON I</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>FARZEELA</t>
+          <t>FARZEELA F</t>
         </is>
       </c>
     </row>
@@ -1235,17 +1235,17 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>SALAM</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>FARZEELA</t>
+          <t>FARZEELA F</t>
         </is>
       </c>
     </row>

--- a/intern_schedule_2026-2027/schedules/TYP_December_2026.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_December_2026.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +32,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <b val="1"/>
       <i val="1"/>
@@ -78,23 +79,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -515,19 +519,19 @@
       <c r="B3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I, VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>SHETTY K</t>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE, SHETTY</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN</t>
         </is>
       </c>
     </row>
@@ -540,19 +544,19 @@
       <c r="B4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>SHETTY K</t>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE, BRONSON</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN</t>
         </is>
       </c>
     </row>
@@ -565,19 +569,19 @@
       <c r="B5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>SHETTY K</t>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN</t>
         </is>
       </c>
     </row>
@@ -590,61 +594,61 @@
       <c r="B6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I, VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>SHETTY K</t>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE, SHETTY</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN S  (24H)</t>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>SHETTY</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>SHETTY  (24H)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>SHETTY K</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -657,19 +661,19 @@
       <c r="B9" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>VILLANUEVA R, VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>VILLANUEVA, MACNEILLE</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -682,19 +686,19 @@
       <c r="B10" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>VILLANUEVA R</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I, VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>VILLANUEVA</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN, MACNEILLE</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -707,19 +711,19 @@
       <c r="B11" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I, VILLANUEVA R</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN, VILLANUEVA</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -732,19 +736,19 @@
       <c r="B12" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>VILLANUEVA R</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>VILLANUEVA</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -757,61 +761,61 @@
       <c r="B13" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>VILLANUEVA R, VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>VILLANUEVA</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN, MACNEILLE</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>VILLANUEVA R</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>VILLANUEVA R  (24H)</t>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>MACNEILLE  (24H)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>VILLANUEVA</t>
         </is>
       </c>
     </row>
@@ -824,19 +828,19 @@
       <c r="B16" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>VILLANUEVA R, SALAM M</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE, SALAM</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>VILLANUEVA</t>
         </is>
       </c>
     </row>
@@ -849,19 +853,19 @@
       <c r="B17" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>SALAM M</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, VILLANUEVA R</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON, SALAM</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>VILLANUEVA</t>
         </is>
       </c>
     </row>
@@ -874,19 +878,19 @@
       <c r="B18" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>VILLANUEVA R</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, SALAM M</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>SALAM</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON, MACNEILLE</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>VILLANUEVA</t>
         </is>
       </c>
     </row>
@@ -899,19 +903,19 @@
       <c r="B19" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>SALAM M</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>VILLANUEVA R</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>VILLANUEVA</t>
         </is>
       </c>
     </row>
@@ -924,61 +928,61 @@
       <c r="B20" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>VILLANUEVA R</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, SALAM M</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON, SALAM</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>VILLANUEVA</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="B21" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>MACNEILLE S  (24H)</t>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>SALAM</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>SALAM  (24H)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>VILLANUEVA R</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>SALAM M</t>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -991,19 +995,19 @@
       <c r="B23" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, FARZEELA F</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>SALAM M</t>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>FARZEELA</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>SALAM, BRONSON</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -1016,19 +1020,19 @@
       <c r="B24" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>FARZEELA F</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, BRONSON I</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>SALAM M</t>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>SALAM</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>FARZEELA, BRONSON</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -1041,19 +1045,19 @@
       <c r="B25" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I, FARZEELA F</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>SALAM M</t>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>FARZEELA, SALAM</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -1066,19 +1070,19 @@
       <c r="B26" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>FARZEELA F</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>SALAM M</t>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>FARZEELA</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>SALAM</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -1091,61 +1095,61 @@
       <c r="B27" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I, FARZEELA F</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>SALAM M</t>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>SALAM</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>FARZEELA, BRONSON</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B28" s="4" t="n">
+      <c r="B28" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>BRONSON I  (24H)</t>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>BRONSON  (24H)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B29" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>SALAM M</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>FARZEELA F</t>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>FARZEELA</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>SALAM</t>
         </is>
       </c>
     </row>
@@ -1158,19 +1162,19 @@
       <c r="B30" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I, SALAM M</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>FARZEELA F</t>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON, FARZEELA</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>SALAM</t>
         </is>
       </c>
     </row>
@@ -1183,19 +1187,19 @@
       <c r="B31" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, SALAM M</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>FARZEELA F</t>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE, FARZEELA</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>SALAM</t>
         </is>
       </c>
     </row>
@@ -1208,19 +1212,19 @@
       <c r="B32" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>SALAM M</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, BRONSON I</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>FARZEELA F</t>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>FARZEELA</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE, BRONSON</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>SALAM</t>
         </is>
       </c>
     </row>
@@ -1233,36 +1237,36 @@
       <c r="B33" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>FARZEELA F</t>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>SALAM</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>INTERNS</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>DATES</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>LSH</t>
         </is>
@@ -1293,7 +1297,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>BMC-S / BRIGHTON</t>
         </is>
@@ -1336,7 +1340,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>LAHEY</t>
         </is>
@@ -1367,7 +1371,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="C49" s="6" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>SENIOR RESIDENT</t>
         </is>
@@ -1410,7 +1414,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t>SHORT CALL DOESN'T LEAVE BEFORE 4 PM, UNLESS APPROVED BY PD/APDS</t>
         </is>

--- a/intern_schedule_2026-2027/schedules/TYP_December_2026.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_December_2026.xlsx
@@ -521,12 +521,12 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE, SHETTY</t>
+          <t>BRONSON, SHETTY</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -551,7 +551,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE, BRONSON</t>
+          <t>BRONSON, MACNEILLE</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -571,12 +571,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE, SHETTY</t>
+          <t>BRONSON, SHETTY</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -642,13 +642,13 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -668,12 +668,12 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>VILLANUEVA, MACNEILLE</t>
+          <t>VILLANUEVA, BRONSON</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -693,12 +693,12 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN, MACNEILLE</t>
+          <t>VIVEKANANDAN, BRONSON</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN, MACNEILLE</t>
+          <t>VIVEKANANDAN, BRONSON</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -788,13 +788,13 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>MACNEILLE  (24H)</t>
+          <t>BRONSON  (24H)</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE, SALAM</t>
+          <t>BRONSON, SALAM</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -855,12 +855,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>BRONSON, SALAM</t>
+          <t>MACNEILLE, SALAM</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>BRONSON, MACNEILLE</t>
+          <t>MACNEILLE, BRONSON</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
           <t>BRONSON</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>MACNEILLE</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>BRONSON, SALAM</t>
+          <t>MACNEILLE, SALAM</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -976,13 +976,13 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
       <c r="D22" s="6" t="n"/>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>SALAM, BRONSON</t>
+          <t>SALAM, MACNEILLE</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>FARZEELA, BRONSON</t>
+          <t>FARZEELA, MACNEILLE</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -1047,17 +1047,17 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>FARZEELA, SALAM</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
           <t>BRONSON</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>FARZEELA, SALAM</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>FARZEELA, BRONSON</t>
+          <t>FARZEELA, MACNEILLE</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -1122,13 +1122,13 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
       <c r="D28" s="5" t="n"/>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>BRONSON  (24H)</t>
+          <t>MACNEILLE  (24H)</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
